--- a/output/version3/test/10-5/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
+++ b/output/version3/test/10-5/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="C2" t="n">
+        <v>451</v>
+      </c>
+      <c r="D2" t="n">
+        <v>465</v>
+      </c>
+      <c r="E2" t="n">
+        <v>460</v>
+      </c>
+      <c r="F2" t="n">
+        <v>432</v>
+      </c>
+      <c r="G2" t="n">
+        <v>553</v>
+      </c>
+      <c r="H2" t="n">
+        <v>453</v>
+      </c>
+      <c r="I2" t="n">
+        <v>455</v>
+      </c>
+      <c r="J2" t="n">
         <v>479</v>
       </c>
-      <c r="D2" t="n">
-        <v>409</v>
-      </c>
-      <c r="E2" t="n">
-        <v>451</v>
-      </c>
-      <c r="F2" t="n">
-        <v>451</v>
-      </c>
-      <c r="G2" t="n">
-        <v>465</v>
-      </c>
-      <c r="H2" t="n">
-        <v>520</v>
-      </c>
-      <c r="I2" t="n">
-        <v>441</v>
-      </c>
-      <c r="J2" t="n">
-        <v>463</v>
-      </c>
       <c r="K2" t="n">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L2" t="n">
-        <v>461.3</v>
+        <v>469.9</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>564</v>
+        <v>433</v>
       </c>
       <c r="C3" t="n">
         <v>493</v>
       </c>
       <c r="D3" t="n">
-        <v>528</v>
+        <v>572</v>
       </c>
       <c r="E3" t="n">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="F3" t="n">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G3" t="n">
-        <v>527</v>
+        <v>446</v>
       </c>
       <c r="H3" t="n">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="I3" t="n">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="J3" t="n">
-        <v>481</v>
+        <v>532</v>
       </c>
       <c r="K3" t="n">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="L3" t="n">
-        <v>505.2</v>
+        <v>498.4</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>479</v>
+        <v>522</v>
       </c>
       <c r="C4" t="n">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="D4" t="n">
-        <v>588</v>
+        <v>463</v>
       </c>
       <c r="E4" t="n">
-        <v>505</v>
+        <v>453</v>
       </c>
       <c r="F4" t="n">
-        <v>469</v>
+        <v>583</v>
       </c>
       <c r="G4" t="n">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="H4" t="n">
-        <v>570</v>
+        <v>504</v>
       </c>
       <c r="I4" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J4" t="n">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="K4" t="n">
-        <v>545</v>
+        <v>497</v>
       </c>
       <c r="L4" t="n">
-        <v>507.9</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="C5" t="n">
-        <v>498</v>
+        <v>422</v>
       </c>
       <c r="D5" t="n">
-        <v>506</v>
+        <v>445</v>
       </c>
       <c r="E5" t="n">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="F5" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G5" t="n">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="H5" t="n">
-        <v>500</v>
+        <v>457</v>
       </c>
       <c r="I5" t="n">
-        <v>485</v>
+        <v>460</v>
       </c>
       <c r="J5" t="n">
-        <v>429</v>
+        <v>504</v>
       </c>
       <c r="K5" t="n">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="L5" t="n">
-        <v>479</v>
+        <v>468.9</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>487</v>
+        <v>442</v>
       </c>
       <c r="C6" t="n">
-        <v>428</v>
+        <v>501</v>
       </c>
       <c r="D6" t="n">
-        <v>440</v>
+        <v>509</v>
       </c>
       <c r="E6" t="n">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="F6" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G6" t="n">
+        <v>418</v>
+      </c>
+      <c r="H6" t="n">
         <v>438</v>
       </c>
-      <c r="H6" t="n">
-        <v>440</v>
-      </c>
       <c r="I6" t="n">
-        <v>430</v>
+        <v>479</v>
       </c>
       <c r="J6" t="n">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="K6" t="n">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="L6" t="n">
-        <v>443.9</v>
+        <v>462.2</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>463</v>
+        <v>371</v>
       </c>
       <c r="C7" t="n">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="D7" t="n">
+        <v>485</v>
+      </c>
+      <c r="E7" t="n">
+        <v>407</v>
+      </c>
+      <c r="F7" t="n">
+        <v>473</v>
+      </c>
+      <c r="G7" t="n">
+        <v>389</v>
+      </c>
+      <c r="H7" t="n">
+        <v>446</v>
+      </c>
+      <c r="I7" t="n">
         <v>433</v>
       </c>
-      <c r="E7" t="n">
-        <v>432</v>
-      </c>
-      <c r="F7" t="n">
-        <v>446</v>
-      </c>
-      <c r="G7" t="n">
-        <v>439</v>
-      </c>
-      <c r="H7" t="n">
-        <v>422</v>
-      </c>
-      <c r="I7" t="n">
-        <v>537</v>
-      </c>
       <c r="J7" t="n">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="K7" t="n">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="L7" t="n">
-        <v>449.1</v>
+        <v>435.1</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>526</v>
+        <v>455</v>
       </c>
       <c r="C8" t="n">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="D8" t="n">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="E8" t="n">
-        <v>517</v>
+        <v>470</v>
       </c>
       <c r="F8" t="n">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="G8" t="n">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="H8" t="n">
-        <v>468</v>
+        <v>514</v>
       </c>
       <c r="I8" t="n">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="J8" t="n">
+        <v>520</v>
+      </c>
+      <c r="K8" t="n">
         <v>497</v>
       </c>
-      <c r="K8" t="n">
-        <v>474</v>
-      </c>
       <c r="L8" t="n">
-        <v>496.8</v>
+        <v>503.6</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C9" t="n">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="D9" t="n">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E9" t="n">
-        <v>412</v>
+        <v>473</v>
       </c>
       <c r="F9" t="n">
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="G9" t="n">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="H9" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="I9" t="n">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="J9" t="n">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="K9" t="n">
-        <v>423</v>
+        <v>480</v>
       </c>
       <c r="L9" t="n">
-        <v>440.6</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="C10" t="n">
-        <v>500</v>
+        <v>441</v>
       </c>
       <c r="D10" t="n">
-        <v>512</v>
+        <v>545</v>
       </c>
       <c r="E10" t="n">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="F10" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G10" t="n">
-        <v>422</v>
+        <v>519</v>
       </c>
       <c r="H10" t="n">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="I10" t="n">
-        <v>497</v>
+        <v>585</v>
       </c>
       <c r="J10" t="n">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="K10" t="n">
-        <v>534</v>
+        <v>496</v>
       </c>
       <c r="L10" t="n">
-        <v>495</v>
+        <v>511.5</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="C11" t="n">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="D11" t="n">
-        <v>464</v>
+        <v>398</v>
       </c>
       <c r="E11" t="n">
-        <v>479</v>
+        <v>440</v>
       </c>
       <c r="F11" t="n">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G11" t="n">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="H11" t="n">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="I11" t="n">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="J11" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="K11" t="n">
         <v>461</v>
       </c>
       <c r="L11" t="n">
-        <v>442.5</v>
+        <v>440.7</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C12" t="n">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="D12" t="n">
-        <v>538</v>
+        <v>495</v>
       </c>
       <c r="E12" t="n">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="F12" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G12" t="n">
-        <v>620</v>
+        <v>522</v>
       </c>
       <c r="H12" t="n">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="I12" t="n">
-        <v>532</v>
+        <v>458</v>
       </c>
       <c r="J12" t="n">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="K12" t="n">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="L12" t="n">
-        <v>530</v>
+        <v>506.8</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="C13" t="n">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="D13" t="n">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="E13" t="n">
-        <v>481</v>
+        <v>537</v>
       </c>
       <c r="F13" t="n">
-        <v>535</v>
+        <v>456</v>
       </c>
       <c r="G13" t="n">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="H13" t="n">
-        <v>503</v>
+        <v>429</v>
       </c>
       <c r="I13" t="n">
-        <v>529</v>
+        <v>493</v>
       </c>
       <c r="J13" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="K13" t="n">
-        <v>479</v>
+        <v>550</v>
       </c>
       <c r="L13" t="n">
-        <v>502.6</v>
+        <v>491.8</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>531</v>
+        <v>481</v>
       </c>
       <c r="C14" t="n">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D14" t="n">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="E14" t="n">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F14" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G14" t="n">
-        <v>549</v>
+        <v>573</v>
       </c>
       <c r="H14" t="n">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="I14" t="n">
-        <v>524</v>
+        <v>429</v>
       </c>
       <c r="J14" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="K14" t="n">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="L14" t="n">
-        <v>523.6</v>
+        <v>511.4</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C15" t="n">
-        <v>471</v>
+        <v>429</v>
       </c>
       <c r="D15" t="n">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="E15" t="n">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="F15" t="n">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="G15" t="n">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="H15" t="n">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="I15" t="n">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J15" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="K15" t="n">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="L15" t="n">
-        <v>458.6</v>
+        <v>457.1</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C16" t="n">
+        <v>458</v>
+      </c>
+      <c r="D16" t="n">
+        <v>514</v>
+      </c>
+      <c r="E16" t="n">
+        <v>514</v>
+      </c>
+      <c r="F16" t="n">
+        <v>491</v>
+      </c>
+      <c r="G16" t="n">
         <v>468</v>
       </c>
-      <c r="D16" t="n">
-        <v>441</v>
-      </c>
-      <c r="E16" t="n">
-        <v>452</v>
-      </c>
-      <c r="F16" t="n">
-        <v>452</v>
-      </c>
-      <c r="G16" t="n">
-        <v>459</v>
-      </c>
       <c r="H16" t="n">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="I16" t="n">
-        <v>444</v>
+        <v>483</v>
       </c>
       <c r="J16" t="n">
         <v>476</v>
       </c>
       <c r="K16" t="n">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="L16" t="n">
-        <v>460.1</v>
+        <v>480.1</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="C17" t="n">
-        <v>445</v>
+        <v>500</v>
       </c>
       <c r="D17" t="n">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="E17" t="n">
+        <v>397</v>
+      </c>
+      <c r="F17" t="n">
+        <v>502</v>
+      </c>
+      <c r="G17" t="n">
+        <v>424</v>
+      </c>
+      <c r="H17" t="n">
+        <v>471</v>
+      </c>
+      <c r="I17" t="n">
         <v>467</v>
       </c>
-      <c r="F17" t="n">
-        <v>419</v>
-      </c>
-      <c r="G17" t="n">
-        <v>502</v>
-      </c>
-      <c r="H17" t="n">
-        <v>429</v>
-      </c>
-      <c r="I17" t="n">
-        <v>427</v>
-      </c>
       <c r="J17" t="n">
-        <v>528</v>
+        <v>383</v>
       </c>
       <c r="K17" t="n">
-        <v>549</v>
+        <v>481</v>
       </c>
       <c r="L17" t="n">
-        <v>467.8</v>
+        <v>453.9</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>517</v>
+        <v>425</v>
       </c>
       <c r="C18" t="n">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="D18" t="n">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="E18" t="n">
-        <v>516</v>
+        <v>435</v>
       </c>
       <c r="F18" t="n">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="G18" t="n">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="H18" t="n">
-        <v>561</v>
+        <v>439</v>
       </c>
       <c r="I18" t="n">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="J18" t="n">
-        <v>459</v>
+        <v>496</v>
       </c>
       <c r="K18" t="n">
-        <v>494</v>
+        <v>553</v>
       </c>
       <c r="L18" t="n">
-        <v>498.5</v>
+        <v>475.1</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
+        <v>508</v>
+      </c>
+      <c r="C19" t="n">
         <v>527</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
+        <v>462</v>
+      </c>
+      <c r="E19" t="n">
+        <v>500</v>
+      </c>
+      <c r="F19" t="n">
+        <v>477</v>
+      </c>
+      <c r="G19" t="n">
         <v>447</v>
       </c>
-      <c r="D19" t="n">
-        <v>501</v>
-      </c>
-      <c r="E19" t="n">
-        <v>463</v>
-      </c>
-      <c r="F19" t="n">
-        <v>567</v>
-      </c>
-      <c r="G19" t="n">
-        <v>537</v>
-      </c>
       <c r="H19" t="n">
-        <v>548</v>
+        <v>522</v>
       </c>
       <c r="I19" t="n">
-        <v>480</v>
+        <v>538</v>
       </c>
       <c r="J19" t="n">
-        <v>538</v>
+        <v>468</v>
       </c>
       <c r="K19" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="L19" t="n">
-        <v>513.6</v>
+        <v>498.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>452</v>
+        <v>542</v>
       </c>
       <c r="C20" t="n">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="D20" t="n">
-        <v>424</v>
+        <v>481</v>
       </c>
       <c r="E20" t="n">
-        <v>470</v>
+        <v>550</v>
       </c>
       <c r="F20" t="n">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="G20" t="n">
-        <v>486</v>
+        <v>439</v>
       </c>
       <c r="H20" t="n">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="I20" t="n">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="J20" t="n">
-        <v>479</v>
+        <v>590</v>
       </c>
       <c r="K20" t="n">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="L20" t="n">
-        <v>475.4</v>
+        <v>510.9</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>536</v>
+        <v>467</v>
       </c>
       <c r="C21" t="n">
-        <v>552</v>
+        <v>462</v>
       </c>
       <c r="D21" t="n">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E21" t="n">
-        <v>453</v>
+        <v>488</v>
       </c>
       <c r="F21" t="n">
-        <v>439</v>
+        <v>404</v>
       </c>
       <c r="G21" t="n">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="H21" t="n">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="I21" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="J21" t="n">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="K21" t="n">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="L21" t="n">
-        <v>477.3</v>
+        <v>466.5</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>428</v>
+        <v>474</v>
       </c>
       <c r="C22" t="n">
-        <v>440</v>
+        <v>499</v>
       </c>
       <c r="D22" t="n">
-        <v>429</v>
+        <v>503</v>
       </c>
       <c r="E22" t="n">
-        <v>467</v>
+        <v>513</v>
       </c>
       <c r="F22" t="n">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="G22" t="n">
-        <v>472</v>
+        <v>405</v>
       </c>
       <c r="H22" t="n">
-        <v>427</v>
+        <v>470</v>
       </c>
       <c r="I22" t="n">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="J22" t="n">
-        <v>559</v>
+        <v>484</v>
       </c>
       <c r="K22" t="n">
-        <v>429</v>
+        <v>462</v>
       </c>
       <c r="L22" t="n">
-        <v>455.6</v>
+        <v>474.7</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="C23" t="n">
-        <v>369</v>
+        <v>451</v>
       </c>
       <c r="D23" t="n">
+        <v>379</v>
+      </c>
+      <c r="E23" t="n">
+        <v>416</v>
+      </c>
+      <c r="F23" t="n">
+        <v>458</v>
+      </c>
+      <c r="G23" t="n">
+        <v>419</v>
+      </c>
+      <c r="H23" t="n">
+        <v>452</v>
+      </c>
+      <c r="I23" t="n">
+        <v>463</v>
+      </c>
+      <c r="J23" t="n">
         <v>424</v>
       </c>
-      <c r="E23" t="n">
-        <v>425</v>
-      </c>
-      <c r="F23" t="n">
-        <v>452</v>
-      </c>
-      <c r="G23" t="n">
-        <v>461</v>
-      </c>
-      <c r="H23" t="n">
-        <v>419</v>
-      </c>
-      <c r="I23" t="n">
-        <v>379</v>
-      </c>
-      <c r="J23" t="n">
-        <v>466</v>
-      </c>
       <c r="K23" t="n">
-        <v>397</v>
+        <v>481</v>
       </c>
       <c r="L23" t="n">
-        <v>422</v>
+        <v>440.3</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C24" t="n">
-        <v>415</v>
+        <v>503</v>
       </c>
       <c r="D24" t="n">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="E24" t="n">
-        <v>410</v>
+        <v>454</v>
       </c>
       <c r="F24" t="n">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="G24" t="n">
-        <v>419</v>
+        <v>371</v>
       </c>
       <c r="H24" t="n">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="I24" t="n">
-        <v>415</v>
+        <v>486</v>
       </c>
       <c r="J24" t="n">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="K24" t="n">
-        <v>419</v>
+        <v>521</v>
       </c>
       <c r="L24" t="n">
-        <v>434.5</v>
+        <v>454.6</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>390</v>
+        <v>421</v>
       </c>
       <c r="C25" t="n">
-        <v>399</v>
+        <v>442</v>
       </c>
       <c r="D25" t="n">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="E25" t="n">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="F25" t="n">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="G25" t="n">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="H25" t="n">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="I25" t="n">
-        <v>454</v>
+        <v>393</v>
       </c>
       <c r="J25" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K25" t="n">
-        <v>374</v>
+        <v>443</v>
       </c>
       <c r="L25" t="n">
-        <v>408.7</v>
+        <v>413.9</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>604</v>
+        <v>580</v>
       </c>
       <c r="C26" t="n">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="D26" t="n">
-        <v>663</v>
+        <v>583</v>
       </c>
       <c r="E26" t="n">
-        <v>567</v>
+        <v>540</v>
       </c>
       <c r="F26" t="n">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="G26" t="n">
-        <v>484</v>
+        <v>579</v>
       </c>
       <c r="H26" t="n">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="I26" t="n">
-        <v>592</v>
+        <v>527</v>
       </c>
       <c r="J26" t="n">
-        <v>493</v>
+        <v>547</v>
       </c>
       <c r="K26" t="n">
-        <v>528</v>
+        <v>574</v>
       </c>
       <c r="L26" t="n">
-        <v>551.8</v>
+        <v>554.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="C27" t="n">
+        <v>459</v>
+      </c>
+      <c r="D27" t="n">
+        <v>419</v>
+      </c>
+      <c r="E27" t="n">
         <v>448</v>
       </c>
-      <c r="D27" t="n">
-        <v>449</v>
-      </c>
-      <c r="E27" t="n">
-        <v>428</v>
-      </c>
       <c r="F27" t="n">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="G27" t="n">
         <v>437</v>
       </c>
       <c r="H27" t="n">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="I27" t="n">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J27" t="n">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="K27" t="n">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="L27" t="n">
-        <v>439.4</v>
+        <v>435.3</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C28" t="n">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="D28" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E28" t="n">
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="F28" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G28" t="n">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="H28" t="n">
+        <v>458</v>
+      </c>
+      <c r="I28" t="n">
+        <v>454</v>
+      </c>
+      <c r="J28" t="n">
         <v>456</v>
       </c>
-      <c r="I28" t="n">
-        <v>465</v>
-      </c>
-      <c r="J28" t="n">
-        <v>458</v>
-      </c>
       <c r="K28" t="n">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="L28" t="n">
-        <v>464.1</v>
+        <v>464.5</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C29" t="n">
-        <v>424</v>
+        <v>386</v>
       </c>
       <c r="D29" t="n">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="E29" t="n">
-        <v>408</v>
+        <v>489</v>
       </c>
       <c r="F29" t="n">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="G29" t="n">
-        <v>428</v>
+        <v>396</v>
       </c>
       <c r="H29" t="n">
-        <v>467</v>
+        <v>429</v>
       </c>
       <c r="I29" t="n">
-        <v>403</v>
+        <v>495</v>
       </c>
       <c r="J29" t="n">
-        <v>439</v>
+        <v>389</v>
       </c>
       <c r="K29" t="n">
-        <v>401</v>
+        <v>445</v>
       </c>
       <c r="L29" t="n">
-        <v>429.5</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>404</v>
+        <v>459</v>
       </c>
       <c r="C30" t="n">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="D30" t="n">
-        <v>413</v>
+        <v>442</v>
       </c>
       <c r="E30" t="n">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="F30" t="n">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="G30" t="n">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="H30" t="n">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="I30" t="n">
-        <v>406</v>
+        <v>451</v>
       </c>
       <c r="J30" t="n">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="K30" t="n">
         <v>435</v>
       </c>
       <c r="L30" t="n">
-        <v>417.3</v>
+        <v>446.3</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="C31" t="n">
-        <v>468</v>
+        <v>400</v>
       </c>
       <c r="D31" t="n">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E31" t="n">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="F31" t="n">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="G31" t="n">
-        <v>488</v>
+        <v>460</v>
       </c>
       <c r="H31" t="n">
-        <v>470</v>
+        <v>513</v>
       </c>
       <c r="I31" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="J31" t="n">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="K31" t="n">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="L31" t="n">
-        <v>453.8</v>
+        <v>448.2</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="C32" t="n">
+        <v>423</v>
+      </c>
+      <c r="D32" t="n">
+        <v>396</v>
+      </c>
+      <c r="E32" t="n">
+        <v>413</v>
+      </c>
+      <c r="F32" t="n">
         <v>426</v>
       </c>
-      <c r="D32" t="n">
-        <v>472</v>
-      </c>
-      <c r="E32" t="n">
-        <v>459</v>
-      </c>
-      <c r="F32" t="n">
-        <v>402</v>
-      </c>
       <c r="G32" t="n">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="H32" t="n">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="I32" t="n">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="J32" t="n">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="K32" t="n">
-        <v>460</v>
+        <v>418</v>
       </c>
       <c r="L32" t="n">
-        <v>443.3</v>
+        <v>426.7</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="C33" t="n">
-        <v>458</v>
+        <v>422</v>
       </c>
       <c r="D33" t="n">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="E33" t="n">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="F33" t="n">
-        <v>375</v>
+        <v>415</v>
       </c>
       <c r="G33" t="n">
-        <v>381</v>
+        <v>432</v>
       </c>
       <c r="H33" t="n">
-        <v>470</v>
+        <v>512</v>
       </c>
       <c r="I33" t="n">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J33" t="n">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="K33" t="n">
-        <v>382</v>
+        <v>474</v>
       </c>
       <c r="L33" t="n">
-        <v>413.3</v>
+        <v>422.6</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="C34" t="n">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="D34" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E34" t="n">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="F34" t="n">
-        <v>454</v>
+        <v>416</v>
       </c>
       <c r="G34" t="n">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="H34" t="n">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="I34" t="n">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="J34" t="n">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="K34" t="n">
-        <v>454</v>
+        <v>387</v>
       </c>
       <c r="L34" t="n">
-        <v>423.1</v>
+        <v>414.3</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>554</v>
+        <v>505</v>
       </c>
       <c r="C35" t="n">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D35" t="n">
+        <v>489</v>
+      </c>
+      <c r="E35" t="n">
+        <v>514</v>
+      </c>
+      <c r="F35" t="n">
         <v>427</v>
       </c>
-      <c r="E35" t="n">
-        <v>497</v>
-      </c>
-      <c r="F35" t="n">
-        <v>507</v>
-      </c>
       <c r="G35" t="n">
-        <v>514</v>
+        <v>415</v>
       </c>
       <c r="H35" t="n">
-        <v>453</v>
+        <v>513</v>
       </c>
       <c r="I35" t="n">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="J35" t="n">
-        <v>468</v>
+        <v>408</v>
       </c>
       <c r="K35" t="n">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="L35" t="n">
-        <v>488.1</v>
+        <v>468.1</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>442</v>
+        <v>371</v>
       </c>
       <c r="C36" t="n">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="D36" t="n">
+        <v>343</v>
+      </c>
+      <c r="E36" t="n">
+        <v>435</v>
+      </c>
+      <c r="F36" t="n">
+        <v>387</v>
+      </c>
+      <c r="G36" t="n">
         <v>371</v>
       </c>
-      <c r="E36" t="n">
-        <v>354</v>
-      </c>
-      <c r="F36" t="n">
-        <v>377</v>
-      </c>
-      <c r="G36" t="n">
-        <v>389</v>
-      </c>
       <c r="H36" t="n">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="I36" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J36" t="n">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="K36" t="n">
-        <v>369</v>
+        <v>423</v>
       </c>
       <c r="L36" t="n">
-        <v>382.6</v>
+        <v>386</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>474</v>
+        <v>430</v>
       </c>
       <c r="C37" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D37" t="n">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E37" t="n">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="F37" t="n">
-        <v>455</v>
+        <v>418</v>
       </c>
       <c r="G37" t="n">
-        <v>445</v>
+        <v>478</v>
       </c>
       <c r="H37" t="n">
-        <v>476</v>
+        <v>423</v>
       </c>
       <c r="I37" t="n">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="J37" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K37" t="n">
-        <v>467</v>
+        <v>416</v>
       </c>
       <c r="L37" t="n">
-        <v>451.9</v>
+        <v>440.1</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="C38" t="n">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="D38" t="n">
-        <v>477</v>
+        <v>533</v>
       </c>
       <c r="E38" t="n">
-        <v>584</v>
+        <v>547</v>
       </c>
       <c r="F38" t="n">
-        <v>580</v>
+        <v>535</v>
       </c>
       <c r="G38" t="n">
-        <v>479</v>
+        <v>671</v>
       </c>
       <c r="H38" t="n">
-        <v>616</v>
+        <v>503</v>
       </c>
       <c r="I38" t="n">
-        <v>492</v>
+        <v>527</v>
       </c>
       <c r="J38" t="n">
-        <v>555</v>
+        <v>471</v>
       </c>
       <c r="K38" t="n">
-        <v>596</v>
+        <v>529</v>
       </c>
       <c r="L38" t="n">
-        <v>537.2</v>
+        <v>537.3</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
+        <v>404</v>
+      </c>
+      <c r="C39" t="n">
+        <v>376</v>
+      </c>
+      <c r="D39" t="n">
+        <v>434</v>
+      </c>
+      <c r="E39" t="n">
+        <v>381</v>
+      </c>
+      <c r="F39" t="n">
+        <v>390</v>
+      </c>
+      <c r="G39" t="n">
+        <v>465</v>
+      </c>
+      <c r="H39" t="n">
+        <v>391</v>
+      </c>
+      <c r="I39" t="n">
+        <v>413</v>
+      </c>
+      <c r="J39" t="n">
+        <v>448</v>
+      </c>
+      <c r="K39" t="n">
         <v>442</v>
       </c>
-      <c r="C39" t="n">
-        <v>404</v>
-      </c>
-      <c r="D39" t="n">
-        <v>428</v>
-      </c>
-      <c r="E39" t="n">
-        <v>468</v>
-      </c>
-      <c r="F39" t="n">
-        <v>450</v>
-      </c>
-      <c r="G39" t="n">
-        <v>382</v>
-      </c>
-      <c r="H39" t="n">
-        <v>381</v>
-      </c>
-      <c r="I39" t="n">
-        <v>450</v>
-      </c>
-      <c r="J39" t="n">
-        <v>406</v>
-      </c>
-      <c r="K39" t="n">
-        <v>361</v>
-      </c>
       <c r="L39" t="n">
-        <v>417.2</v>
+        <v>414.4</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="C40" t="n">
+        <v>479</v>
+      </c>
+      <c r="D40" t="n">
+        <v>482</v>
+      </c>
+      <c r="E40" t="n">
+        <v>494</v>
+      </c>
+      <c r="F40" t="n">
+        <v>444</v>
+      </c>
+      <c r="G40" t="n">
+        <v>501</v>
+      </c>
+      <c r="H40" t="n">
+        <v>432</v>
+      </c>
+      <c r="I40" t="n">
+        <v>494</v>
+      </c>
+      <c r="J40" t="n">
         <v>487</v>
       </c>
-      <c r="D40" t="n">
-        <v>457</v>
-      </c>
-      <c r="E40" t="n">
-        <v>404</v>
-      </c>
-      <c r="F40" t="n">
-        <v>486</v>
-      </c>
-      <c r="G40" t="n">
-        <v>460</v>
-      </c>
-      <c r="H40" t="n">
-        <v>508</v>
-      </c>
-      <c r="I40" t="n">
-        <v>403</v>
-      </c>
-      <c r="J40" t="n">
-        <v>449</v>
-      </c>
       <c r="K40" t="n">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="L40" t="n">
-        <v>463.1</v>
+        <v>472</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>521</v>
+        <v>468</v>
       </c>
       <c r="C41" t="n">
-        <v>473</v>
+        <v>558</v>
       </c>
       <c r="D41" t="n">
-        <v>440</v>
+        <v>485</v>
       </c>
       <c r="E41" t="n">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="F41" t="n">
-        <v>453</v>
+        <v>506</v>
       </c>
       <c r="G41" t="n">
-        <v>534</v>
+        <v>433</v>
       </c>
       <c r="H41" t="n">
-        <v>554</v>
+        <v>466</v>
       </c>
       <c r="I41" t="n">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="J41" t="n">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="K41" t="n">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="L41" t="n">
-        <v>504.2</v>
+        <v>490.6</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
+        <v>473</v>
+      </c>
+      <c r="C42" t="n">
         <v>500</v>
       </c>
-      <c r="C42" t="n">
-        <v>480</v>
-      </c>
       <c r="D42" t="n">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E42" t="n">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="F42" t="n">
-        <v>488</v>
+        <v>528</v>
       </c>
       <c r="G42" t="n">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="H42" t="n">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="I42" t="n">
-        <v>431</v>
+        <v>497</v>
       </c>
       <c r="J42" t="n">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="K42" t="n">
-        <v>456</v>
+        <v>418</v>
       </c>
       <c r="L42" t="n">
-        <v>470</v>
+        <v>474.1</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="C43" t="n">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="D43" t="n">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="E43" t="n">
+        <v>460</v>
+      </c>
+      <c r="F43" t="n">
+        <v>480</v>
+      </c>
+      <c r="G43" t="n">
         <v>453</v>
       </c>
-      <c r="F43" t="n">
-        <v>484</v>
-      </c>
-      <c r="G43" t="n">
-        <v>460</v>
-      </c>
       <c r="H43" t="n">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="I43" t="n">
-        <v>430</v>
+        <v>482</v>
       </c>
       <c r="J43" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="K43" t="n">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="L43" t="n">
-        <v>463.2</v>
+        <v>463.4</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="C44" t="n">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D44" t="n">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="E44" t="n">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="F44" t="n">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="G44" t="n">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="H44" t="n">
-        <v>434</v>
+        <v>476</v>
       </c>
       <c r="I44" t="n">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="J44" t="n">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="K44" t="n">
-        <v>436</v>
+        <v>519</v>
       </c>
       <c r="L44" t="n">
-        <v>448.6</v>
+        <v>471.7</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="C45" t="n">
-        <v>401</v>
+        <v>493</v>
       </c>
       <c r="D45" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E45" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F45" t="n">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="G45" t="n">
-        <v>368</v>
+        <v>462</v>
       </c>
       <c r="H45" t="n">
-        <v>485</v>
+        <v>557</v>
       </c>
       <c r="I45" t="n">
-        <v>420</v>
+        <v>469</v>
       </c>
       <c r="J45" t="n">
-        <v>504</v>
+        <v>393</v>
       </c>
       <c r="K45" t="n">
-        <v>504</v>
+        <v>549</v>
       </c>
       <c r="L45" t="n">
-        <v>449.2</v>
+        <v>473.5</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="C46" t="n">
-        <v>431</v>
+        <v>371</v>
       </c>
       <c r="D46" t="n">
-        <v>335</v>
+        <v>375</v>
       </c>
       <c r="E46" t="n">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="F46" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="G46" t="n">
         <v>436</v>
       </c>
       <c r="H46" t="n">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="I46" t="n">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J46" t="n">
-        <v>403</v>
+        <v>444</v>
       </c>
       <c r="K46" t="n">
-        <v>351</v>
+        <v>401</v>
       </c>
       <c r="L46" t="n">
-        <v>383.5</v>
+        <v>389.1</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="C47" t="n">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="D47" t="n">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E47" t="n">
-        <v>472</v>
+        <v>546</v>
       </c>
       <c r="F47" t="n">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="G47" t="n">
-        <v>506</v>
+        <v>587</v>
       </c>
       <c r="H47" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I47" t="n">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="J47" t="n">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="K47" t="n">
-        <v>553</v>
+        <v>452</v>
       </c>
       <c r="L47" t="n">
-        <v>520.1</v>
+        <v>518.2</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="C48" t="n">
-        <v>442</v>
+        <v>538</v>
       </c>
       <c r="D48" t="n">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="E48" t="n">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="F48" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="G48" t="n">
-        <v>564</v>
+        <v>496</v>
       </c>
       <c r="H48" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="I48" t="n">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="J48" t="n">
-        <v>528</v>
+        <v>487</v>
       </c>
       <c r="K48" t="n">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="L48" t="n">
-        <v>503.4</v>
+        <v>506.1</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>531</v>
+        <v>463</v>
       </c>
       <c r="C49" t="n">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="D49" t="n">
-        <v>425</v>
+        <v>471</v>
       </c>
       <c r="E49" t="n">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="F49" t="n">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="G49" t="n">
-        <v>595</v>
+        <v>422</v>
       </c>
       <c r="H49" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="I49" t="n">
-        <v>513</v>
+        <v>419</v>
       </c>
       <c r="J49" t="n">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="K49" t="n">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="L49" t="n">
-        <v>474.7</v>
+        <v>448.9</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="C50" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="D50" t="n">
+        <v>406</v>
+      </c>
+      <c r="E50" t="n">
         <v>456</v>
       </c>
-      <c r="E50" t="n">
-        <v>415</v>
-      </c>
       <c r="F50" t="n">
-        <v>429</v>
+        <v>470</v>
       </c>
       <c r="G50" t="n">
+        <v>440</v>
+      </c>
+      <c r="H50" t="n">
         <v>413</v>
       </c>
-      <c r="H50" t="n">
-        <v>406</v>
-      </c>
       <c r="I50" t="n">
-        <v>429</v>
+        <v>475</v>
       </c>
       <c r="J50" t="n">
-        <v>494</v>
+        <v>375</v>
       </c>
       <c r="K50" t="n">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="L50" t="n">
-        <v>431</v>
+        <v>437.7</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C51" t="n">
-        <v>452</v>
+        <v>392</v>
       </c>
       <c r="D51" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E51" t="n">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="F51" t="n">
-        <v>397</v>
+        <v>431</v>
       </c>
       <c r="G51" t="n">
-        <v>399</v>
+        <v>439</v>
       </c>
       <c r="H51" t="n">
-        <v>434</v>
+        <v>393</v>
       </c>
       <c r="I51" t="n">
-        <v>446</v>
+        <v>400</v>
       </c>
       <c r="J51" t="n">
-        <v>481</v>
+        <v>442</v>
       </c>
       <c r="K51" t="n">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="L51" t="n">
-        <v>428.4</v>
+        <v>416.4</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>470.38</v>
+        <v>458.66</v>
       </c>
       <c r="C52" t="n">
-        <v>457.32</v>
+        <v>466.48</v>
       </c>
       <c r="D52" t="n">
-        <v>461.3</v>
+        <v>464.94</v>
       </c>
       <c r="E52" t="n">
-        <v>458.62</v>
+        <v>465.62</v>
       </c>
       <c r="F52" t="n">
-        <v>464.54</v>
+        <v>463.66</v>
       </c>
       <c r="G52" t="n">
-        <v>463.38</v>
+        <v>462.28</v>
       </c>
       <c r="H52" t="n">
-        <v>470.3</v>
+        <v>464.72</v>
       </c>
       <c r="I52" t="n">
-        <v>461.08</v>
+        <v>466.04</v>
       </c>
       <c r="J52" t="n">
-        <v>466.98</v>
+        <v>463.76</v>
       </c>
       <c r="K52" t="n">
-        <v>466.42</v>
+        <v>471.88</v>
       </c>
       <c r="L52" t="n">
-        <v>464.032</v>
+        <v>464.804</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.794565439224243</v>
+        <v>2.3066725730896</v>
       </c>
       <c r="C2" t="n">
-        <v>2.858234882354736</v>
+        <v>2.211153984069824</v>
       </c>
       <c r="D2" t="n">
-        <v>3.736674785614014</v>
+        <v>2.525720596313477</v>
       </c>
       <c r="E2" t="n">
-        <v>2.382659912109375</v>
+        <v>2.475006103515625</v>
       </c>
       <c r="F2" t="n">
-        <v>2.823553562164307</v>
+        <v>2.179685115814209</v>
       </c>
       <c r="G2" t="n">
-        <v>2.433755159378052</v>
+        <v>3.335552215576172</v>
       </c>
       <c r="H2" t="n">
-        <v>2.49293851852417</v>
+        <v>2.344291687011719</v>
       </c>
       <c r="I2" t="n">
-        <v>2.136728763580322</v>
+        <v>2.21414041519165</v>
       </c>
       <c r="J2" t="n">
-        <v>2.110485076904297</v>
+        <v>2.468633413314819</v>
       </c>
       <c r="K2" t="n">
-        <v>2.243825435638428</v>
+        <v>2.455442667007446</v>
       </c>
       <c r="L2" t="n">
-        <v>2.601342153549195</v>
+        <v>2.451629877090454</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.483757019042969</v>
+        <v>2.364896535873413</v>
       </c>
       <c r="C3" t="n">
-        <v>2.372312784194946</v>
+        <v>2.381733894348145</v>
       </c>
       <c r="D3" t="n">
-        <v>4.06957745552063</v>
+        <v>2.620158195495605</v>
       </c>
       <c r="E3" t="n">
-        <v>2.880673170089722</v>
+        <v>2.502692937850952</v>
       </c>
       <c r="F3" t="n">
-        <v>2.228881359100342</v>
+        <v>2.330990314483643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.776094913482666</v>
+        <v>2.492807626724243</v>
       </c>
       <c r="H3" t="n">
-        <v>2.613369941711426</v>
+        <v>2.512563705444336</v>
       </c>
       <c r="I3" t="n">
-        <v>2.213375329971313</v>
+        <v>2.490109205245972</v>
       </c>
       <c r="J3" t="n">
-        <v>2.179471969604492</v>
+        <v>2.726325988769531</v>
       </c>
       <c r="K3" t="n">
-        <v>2.272713184356689</v>
+        <v>2.286288022994995</v>
       </c>
       <c r="L3" t="n">
-        <v>2.60902271270752</v>
+        <v>2.470856642723084</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>2.201405048370361</v>
+        <v>2.510127067565918</v>
       </c>
       <c r="C4" t="n">
-        <v>2.236308097839355</v>
+        <v>2.548220872879028</v>
       </c>
       <c r="D4" t="n">
-        <v>2.588399171829224</v>
+        <v>2.425787687301636</v>
       </c>
       <c r="E4" t="n">
-        <v>2.473217487335205</v>
+        <v>2.566824436187744</v>
       </c>
       <c r="F4" t="n">
-        <v>2.240308523178101</v>
+        <v>2.569202899932861</v>
       </c>
       <c r="G4" t="n">
-        <v>2.496168613433838</v>
+        <v>2.526490688323975</v>
       </c>
       <c r="H4" t="n">
-        <v>2.228328466415405</v>
+        <v>2.678920030593872</v>
       </c>
       <c r="I4" t="n">
-        <v>2.291660308837891</v>
+        <v>2.716089487075806</v>
       </c>
       <c r="J4" t="n">
-        <v>2.134056568145752</v>
+        <v>3.593441247940063</v>
       </c>
       <c r="K4" t="n">
-        <v>2.290671825408936</v>
+        <v>2.486657381057739</v>
       </c>
       <c r="L4" t="n">
-        <v>2.318052411079407</v>
+        <v>2.662176179885864</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1.990927934646606</v>
+        <v>2.132059574127197</v>
       </c>
       <c r="C5" t="n">
-        <v>2.163516998291016</v>
+        <v>2.208370923995972</v>
       </c>
       <c r="D5" t="n">
-        <v>2.036798715591431</v>
+        <v>2.153003215789795</v>
       </c>
       <c r="E5" t="n">
-        <v>2.004888534545898</v>
+        <v>2.341040849685669</v>
       </c>
       <c r="F5" t="n">
-        <v>2.023841381072998</v>
+        <v>2.156988859176636</v>
       </c>
       <c r="G5" t="n">
-        <v>1.925593852996826</v>
+        <v>2.205367565155029</v>
       </c>
       <c r="H5" t="n">
-        <v>2.030347347259521</v>
+        <v>2.141549587249756</v>
       </c>
       <c r="I5" t="n">
-        <v>2.189930200576782</v>
+        <v>2.190417766571045</v>
       </c>
       <c r="J5" t="n">
-        <v>2.090199708938599</v>
+        <v>2.262388467788696</v>
       </c>
       <c r="K5" t="n">
-        <v>2.04429817199707</v>
+        <v>2.183436870574951</v>
       </c>
       <c r="L5" t="n">
-        <v>2.050034284591675</v>
+        <v>2.197462368011474</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>2.04478931427002</v>
+        <v>1.867747068405151</v>
       </c>
       <c r="C6" t="n">
-        <v>1.775476455688477</v>
+        <v>2.082682609558105</v>
       </c>
       <c r="D6" t="n">
-        <v>1.859259843826294</v>
+        <v>2.20536994934082</v>
       </c>
       <c r="E6" t="n">
-        <v>1.882707595825195</v>
+        <v>1.952031373977661</v>
       </c>
       <c r="F6" t="n">
-        <v>1.794424295425415</v>
+        <v>1.933576822280884</v>
       </c>
       <c r="G6" t="n">
-        <v>1.79143500328064</v>
+        <v>1.874716520309448</v>
       </c>
       <c r="H6" t="n">
-        <v>1.779465198516846</v>
+        <v>2.824874877929688</v>
       </c>
       <c r="I6" t="n">
-        <v>1.759005784988403</v>
+        <v>3.213754892349243</v>
       </c>
       <c r="J6" t="n">
-        <v>1.831844329833984</v>
+        <v>2.668421030044556</v>
       </c>
       <c r="K6" t="n">
-        <v>1.749040603637695</v>
+        <v>2.169835567474365</v>
       </c>
       <c r="L6" t="n">
-        <v>1.826744842529297</v>
+        <v>2.279301071166992</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.123088836669922</v>
+        <v>2.544830322265625</v>
       </c>
       <c r="C7" t="n">
-        <v>2.19442892074585</v>
+        <v>2.43691086769104</v>
       </c>
       <c r="D7" t="n">
-        <v>2.238295555114746</v>
+        <v>2.405288696289062</v>
       </c>
       <c r="E7" t="n">
-        <v>2.151530742645264</v>
+        <v>2.34009838104248</v>
       </c>
       <c r="F7" t="n">
-        <v>2.452762603759766</v>
+        <v>2.351879596710205</v>
       </c>
       <c r="G7" t="n">
-        <v>2.138553857803345</v>
+        <v>2.490486145019531</v>
       </c>
       <c r="H7" t="n">
-        <v>2.158986330032349</v>
+        <v>2.551626443862915</v>
       </c>
       <c r="I7" t="n">
-        <v>2.154535055160522</v>
+        <v>2.537079334259033</v>
       </c>
       <c r="J7" t="n">
-        <v>2.13405179977417</v>
+        <v>2.396466970443726</v>
       </c>
       <c r="K7" t="n">
-        <v>2.106204986572266</v>
+        <v>2.422215938568115</v>
       </c>
       <c r="L7" t="n">
-        <v>2.18524386882782</v>
+        <v>2.447688269615173</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>2.277187585830688</v>
+        <v>2.556133270263672</v>
       </c>
       <c r="C8" t="n">
-        <v>2.275705814361572</v>
+        <v>2.352173566818237</v>
       </c>
       <c r="D8" t="n">
-        <v>2.16049599647522</v>
+        <v>2.418143033981323</v>
       </c>
       <c r="E8" t="n">
-        <v>2.275194883346558</v>
+        <v>2.564019441604614</v>
       </c>
       <c r="F8" t="n">
-        <v>2.156507730484009</v>
+        <v>2.604393243789673</v>
       </c>
       <c r="G8" t="n">
-        <v>2.142041683197021</v>
+        <v>2.606909275054932</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2173752784729</v>
+        <v>2.504084825515747</v>
       </c>
       <c r="I8" t="n">
-        <v>2.59539008140564</v>
+        <v>2.640563726425171</v>
       </c>
       <c r="J8" t="n">
-        <v>2.22034740447998</v>
+        <v>2.542204856872559</v>
       </c>
       <c r="K8" t="n">
-        <v>2.175469398498535</v>
+        <v>2.472177028656006</v>
       </c>
       <c r="L8" t="n">
-        <v>2.249571585655212</v>
+        <v>2.526080226898193</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>2.08618688583374</v>
+        <v>2.374300241470337</v>
       </c>
       <c r="C9" t="n">
-        <v>2.204386234283447</v>
+        <v>2.363033533096313</v>
       </c>
       <c r="D9" t="n">
-        <v>2.052751302719116</v>
+        <v>2.421120405197144</v>
       </c>
       <c r="E9" t="n">
-        <v>2.150542497634888</v>
+        <v>2.409013509750366</v>
       </c>
       <c r="F9" t="n">
-        <v>2.163980960845947</v>
+        <v>2.260539293289185</v>
       </c>
       <c r="G9" t="n">
-        <v>2.027345657348633</v>
+        <v>2.245682716369629</v>
       </c>
       <c r="H9" t="n">
-        <v>2.104144334793091</v>
+        <v>2.32940411567688</v>
       </c>
       <c r="I9" t="n">
-        <v>2.177424669265747</v>
+        <v>2.385918855667114</v>
       </c>
       <c r="J9" t="n">
-        <v>2.34989857673645</v>
+        <v>2.574064970016479</v>
       </c>
       <c r="K9" t="n">
-        <v>2.124975204467773</v>
+        <v>2.398447751998901</v>
       </c>
       <c r="L9" t="n">
-        <v>2.144163632392883</v>
+        <v>2.376152539253235</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.622193813323975</v>
+        <v>2.549803018569946</v>
       </c>
       <c r="C10" t="n">
-        <v>2.833664417266846</v>
+        <v>2.404394626617432</v>
       </c>
       <c r="D10" t="n">
-        <v>2.344134092330933</v>
+        <v>2.379939794540405</v>
       </c>
       <c r="E10" t="n">
-        <v>2.139047622680664</v>
+        <v>2.50809121131897</v>
       </c>
       <c r="F10" t="n">
-        <v>2.229346990585327</v>
+        <v>2.741621017456055</v>
       </c>
       <c r="G10" t="n">
-        <v>2.166501522064209</v>
+        <v>2.671290159225464</v>
       </c>
       <c r="H10" t="n">
-        <v>2.162498235702515</v>
+        <v>2.813838720321655</v>
       </c>
       <c r="I10" t="n">
-        <v>2.251270055770874</v>
+        <v>2.561526536941528</v>
       </c>
       <c r="J10" t="n">
-        <v>2.214355707168579</v>
+        <v>2.517896413803101</v>
       </c>
       <c r="K10" t="n">
-        <v>2.28769326210022</v>
+        <v>2.770042896270752</v>
       </c>
       <c r="L10" t="n">
-        <v>2.325070571899414</v>
+        <v>2.591844439506531</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1.916611433029175</v>
+        <v>2.0948166847229</v>
       </c>
       <c r="C11" t="n">
-        <v>1.816888332366943</v>
+        <v>2.054519891738892</v>
       </c>
       <c r="D11" t="n">
-        <v>1.863265514373779</v>
+        <v>2.129234552383423</v>
       </c>
       <c r="E11" t="n">
-        <v>1.837316274642944</v>
+        <v>2.084327936172485</v>
       </c>
       <c r="F11" t="n">
-        <v>1.806905746459961</v>
+        <v>2.102588653564453</v>
       </c>
       <c r="G11" t="n">
-        <v>1.841334104537964</v>
+        <v>2.016063451766968</v>
       </c>
       <c r="H11" t="n">
-        <v>1.819365978240967</v>
+        <v>1.96603536605835</v>
       </c>
       <c r="I11" t="n">
-        <v>1.93855094909668</v>
+        <v>2.075334787368774</v>
       </c>
       <c r="J11" t="n">
-        <v>1.752538442611694</v>
+        <v>2.11102819442749</v>
       </c>
       <c r="K11" t="n">
-        <v>1.837311744689941</v>
+        <v>1.99617338180542</v>
       </c>
       <c r="L11" t="n">
-        <v>1.843008852005005</v>
+        <v>2.063012290000915</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>2.222347497940063</v>
+        <v>2.305399656295776</v>
       </c>
       <c r="C12" t="n">
-        <v>2.056270122528076</v>
+        <v>2.551612615585327</v>
       </c>
       <c r="D12" t="n">
-        <v>2.077210903167725</v>
+        <v>2.29302453994751</v>
       </c>
       <c r="E12" t="n">
-        <v>2.056736469268799</v>
+        <v>2.412230491638184</v>
       </c>
       <c r="F12" t="n">
-        <v>2.066235542297363</v>
+        <v>2.525271892547607</v>
       </c>
       <c r="G12" t="n">
-        <v>2.391905307769775</v>
+        <v>2.284117698669434</v>
       </c>
       <c r="H12" t="n">
-        <v>2.155003070831299</v>
+        <v>2.598542451858521</v>
       </c>
       <c r="I12" t="n">
-        <v>2.229307174682617</v>
+        <v>2.444792985916138</v>
       </c>
       <c r="J12" t="n">
-        <v>2.084184169769287</v>
+        <v>2.247046947479248</v>
       </c>
       <c r="K12" t="n">
-        <v>2.036814451217651</v>
+        <v>2.385255098342896</v>
       </c>
       <c r="L12" t="n">
-        <v>2.137601470947266</v>
+        <v>2.404729437828064</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2.430356979370117</v>
+        <v>2.513694524765015</v>
       </c>
       <c r="C13" t="n">
-        <v>2.160985469818115</v>
+        <v>2.441284418106079</v>
       </c>
       <c r="D13" t="n">
-        <v>2.162495374679565</v>
+        <v>2.358253717422485</v>
       </c>
       <c r="E13" t="n">
-        <v>1.968472242355347</v>
+        <v>2.602218866348267</v>
       </c>
       <c r="F13" t="n">
-        <v>2.378936290740967</v>
+        <v>2.460213422775269</v>
       </c>
       <c r="G13" t="n">
-        <v>2.492166996002197</v>
+        <v>2.480090856552124</v>
       </c>
       <c r="H13" t="n">
-        <v>2.099151372909546</v>
+        <v>2.399739742279053</v>
       </c>
       <c r="I13" t="n">
-        <v>2.160492658615112</v>
+        <v>2.420848608016968</v>
       </c>
       <c r="J13" t="n">
-        <v>2.127079963684082</v>
+        <v>2.408908128738403</v>
       </c>
       <c r="K13" t="n">
-        <v>2.178948163986206</v>
+        <v>2.633065462112427</v>
       </c>
       <c r="L13" t="n">
-        <v>2.215908551216125</v>
+        <v>2.471831774711609</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>2.100634336471558</v>
+        <v>2.462896347045898</v>
       </c>
       <c r="C14" t="n">
-        <v>2.122604131698608</v>
+        <v>2.514556407928467</v>
       </c>
       <c r="D14" t="n">
-        <v>2.381431579589844</v>
+        <v>2.580332279205322</v>
       </c>
       <c r="E14" t="n">
-        <v>2.182446241378784</v>
+        <v>2.463917255401611</v>
       </c>
       <c r="F14" t="n">
-        <v>2.221343755722046</v>
+        <v>2.98200535774231</v>
       </c>
       <c r="G14" t="n">
-        <v>2.208375930786133</v>
+        <v>2.662821769714355</v>
       </c>
       <c r="H14" t="n">
-        <v>2.225849866867065</v>
+        <v>2.741229057312012</v>
       </c>
       <c r="I14" t="n">
-        <v>2.49463677406311</v>
+        <v>2.361048698425293</v>
       </c>
       <c r="J14" t="n">
-        <v>2.277694463729858</v>
+        <v>2.451588153839111</v>
       </c>
       <c r="K14" t="n">
-        <v>2.188417911529541</v>
+        <v>2.58465051651001</v>
       </c>
       <c r="L14" t="n">
-        <v>2.240343499183655</v>
+        <v>2.580504584312439</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1.968981266021729</v>
+        <v>2.169499158859253</v>
       </c>
       <c r="C15" t="n">
-        <v>2.039799451828003</v>
+        <v>2.251693487167358</v>
       </c>
       <c r="D15" t="n">
-        <v>2.023850440979004</v>
+        <v>2.330599784851074</v>
       </c>
       <c r="E15" t="n">
-        <v>2.182462930679321</v>
+        <v>2.328686714172363</v>
       </c>
       <c r="F15" t="n">
-        <v>2.058748722076416</v>
+        <v>2.218335151672363</v>
       </c>
       <c r="G15" t="n">
-        <v>2.028338670730591</v>
+        <v>2.209539413452148</v>
       </c>
       <c r="H15" t="n">
-        <v>2.001911878585815</v>
+        <v>2.279416799545288</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3575119972229</v>
+        <v>2.129697799682617</v>
       </c>
       <c r="J15" t="n">
-        <v>2.101146697998047</v>
+        <v>2.294743537902832</v>
       </c>
       <c r="K15" t="n">
-        <v>1.971980571746826</v>
+        <v>2.362281322479248</v>
       </c>
       <c r="L15" t="n">
-        <v>2.073473262786865</v>
+        <v>2.257449316978454</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>2.07520866394043</v>
+        <v>2.296249389648438</v>
       </c>
       <c r="C16" t="n">
-        <v>2.213363647460938</v>
+        <v>2.484385967254639</v>
       </c>
       <c r="D16" t="n">
-        <v>2.145024299621582</v>
+        <v>2.500822067260742</v>
       </c>
       <c r="E16" t="n">
-        <v>2.553502321243286</v>
+        <v>2.238615274429321</v>
       </c>
       <c r="F16" t="n">
-        <v>2.203381061553955</v>
+        <v>2.418731451034546</v>
       </c>
       <c r="G16" t="n">
-        <v>2.096662521362305</v>
+        <v>2.346493482589722</v>
       </c>
       <c r="H16" t="n">
-        <v>2.332076549530029</v>
+        <v>2.420598745346069</v>
       </c>
       <c r="I16" t="n">
-        <v>2.326577663421631</v>
+        <v>2.464847803115845</v>
       </c>
       <c r="J16" t="n">
-        <v>2.290668249130249</v>
+        <v>2.621359825134277</v>
       </c>
       <c r="K16" t="n">
-        <v>2.244272947311401</v>
+        <v>2.357560634613037</v>
       </c>
       <c r="L16" t="n">
-        <v>2.248073792457581</v>
+        <v>2.414966464042664</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>2.179450273513794</v>
+        <v>2.214291095733643</v>
       </c>
       <c r="C17" t="n">
-        <v>1.902652263641357</v>
+        <v>2.323269605636597</v>
       </c>
       <c r="D17" t="n">
-        <v>2.102148294448853</v>
+        <v>2.272176742553711</v>
       </c>
       <c r="E17" t="n">
-        <v>2.06572699546814</v>
+        <v>2.248537540435791</v>
       </c>
       <c r="F17" t="n">
-        <v>2.03434419631958</v>
+        <v>2.407795190811157</v>
       </c>
       <c r="G17" t="n">
-        <v>1.960493803024292</v>
+        <v>2.495463609695435</v>
       </c>
       <c r="H17" t="n">
-        <v>1.903661727905273</v>
+        <v>2.260147094726562</v>
       </c>
       <c r="I17" t="n">
-        <v>2.206393957138062</v>
+        <v>2.200998067855835</v>
       </c>
       <c r="J17" t="n">
-        <v>2.072227239608765</v>
+        <v>2.162673950195312</v>
       </c>
       <c r="K17" t="n">
-        <v>2.273713350296021</v>
+        <v>2.501380443572998</v>
       </c>
       <c r="L17" t="n">
-        <v>2.070081210136414</v>
+        <v>2.308673334121704</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>2.221343040466309</v>
+        <v>2.410167217254639</v>
       </c>
       <c r="C18" t="n">
-        <v>2.277704238891602</v>
+        <v>2.595344305038452</v>
       </c>
       <c r="D18" t="n">
-        <v>2.276200294494629</v>
+        <v>2.574159860610962</v>
       </c>
       <c r="E18" t="n">
-        <v>2.276699781417847</v>
+        <v>2.482154130935669</v>
       </c>
       <c r="F18" t="n">
-        <v>2.334562301635742</v>
+        <v>2.674145936965942</v>
       </c>
       <c r="G18" t="n">
-        <v>2.352021932601929</v>
+        <v>2.406595945358276</v>
       </c>
       <c r="H18" t="n">
-        <v>2.330563068389893</v>
+        <v>2.434668064117432</v>
       </c>
       <c r="I18" t="n">
-        <v>2.186436653137207</v>
+        <v>2.430778741836548</v>
       </c>
       <c r="J18" t="n">
-        <v>2.286672592163086</v>
+        <v>2.514663219451904</v>
       </c>
       <c r="K18" t="n">
-        <v>2.453742504119873</v>
+        <v>2.766842126846313</v>
       </c>
       <c r="L18" t="n">
-        <v>2.299594640731812</v>
+        <v>2.528951954841614</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>2.223327398300171</v>
+        <v>2.31578516960144</v>
       </c>
       <c r="C19" t="n">
-        <v>2.001897811889648</v>
+        <v>2.292328834533691</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0981605052948</v>
+        <v>2.321087121963501</v>
       </c>
       <c r="E19" t="n">
-        <v>2.331549644470215</v>
+        <v>2.454046487808228</v>
       </c>
       <c r="F19" t="n">
-        <v>2.170489311218262</v>
+        <v>2.266788244247437</v>
       </c>
       <c r="G19" t="n">
-        <v>2.239293813705444</v>
+        <v>2.489389896392822</v>
       </c>
       <c r="H19" t="n">
-        <v>2.234814882278442</v>
+        <v>2.698326110839844</v>
       </c>
       <c r="I19" t="n">
-        <v>2.191412210464478</v>
+        <v>2.41244101524353</v>
       </c>
       <c r="J19" t="n">
-        <v>2.342521190643311</v>
+        <v>2.546688079833984</v>
       </c>
       <c r="K19" t="n">
-        <v>2.377963304519653</v>
+        <v>2.589769124984741</v>
       </c>
       <c r="L19" t="n">
-        <v>2.221143007278442</v>
+        <v>2.438665008544922</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>2.200397729873657</v>
+        <v>2.794882535934448</v>
       </c>
       <c r="C20" t="n">
-        <v>2.143036603927612</v>
+        <v>2.613466024398804</v>
       </c>
       <c r="D20" t="n">
-        <v>1.969997882843018</v>
+        <v>2.400541305541992</v>
       </c>
       <c r="E20" t="n">
-        <v>1.957511901855469</v>
+        <v>2.437682151794434</v>
       </c>
       <c r="F20" t="n">
-        <v>2.119102954864502</v>
+        <v>2.406184911727905</v>
       </c>
       <c r="G20" t="n">
-        <v>2.262733936309814</v>
+        <v>2.163679838180542</v>
       </c>
       <c r="H20" t="n">
-        <v>2.209366083145142</v>
+        <v>2.453650712966919</v>
       </c>
       <c r="I20" t="n">
-        <v>2.153008460998535</v>
+        <v>2.448081970214844</v>
       </c>
       <c r="J20" t="n">
-        <v>2.177453279495239</v>
+        <v>2.853471279144287</v>
       </c>
       <c r="K20" t="n">
-        <v>2.322589635848999</v>
+        <v>2.682548046112061</v>
       </c>
       <c r="L20" t="n">
-        <v>2.151519846916199</v>
+        <v>2.525418877601624</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>2.245779037475586</v>
+        <v>2.300535202026367</v>
       </c>
       <c r="C21" t="n">
-        <v>2.49714994430542</v>
+        <v>2.507761240005493</v>
       </c>
       <c r="D21" t="n">
-        <v>2.143038988113403</v>
+        <v>2.613938093185425</v>
       </c>
       <c r="E21" t="n">
-        <v>2.146566152572632</v>
+        <v>2.591752767562866</v>
       </c>
       <c r="F21" t="n">
-        <v>2.168964862823486</v>
+        <v>2.361615896224976</v>
       </c>
       <c r="G21" t="n">
-        <v>2.246785640716553</v>
+        <v>2.834434509277344</v>
       </c>
       <c r="H21" t="n">
-        <v>2.211366891860962</v>
+        <v>2.581408500671387</v>
       </c>
       <c r="I21" t="n">
-        <v>2.214353322982788</v>
+        <v>2.645662784576416</v>
       </c>
       <c r="J21" t="n">
-        <v>2.242279052734375</v>
+        <v>2.333623886108398</v>
       </c>
       <c r="K21" t="n">
-        <v>2.244790077209473</v>
+        <v>2.655129194259644</v>
       </c>
       <c r="L21" t="n">
-        <v>2.236107397079468</v>
+        <v>2.542586207389832</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>2.019853591918945</v>
+        <v>2.230622529983521</v>
       </c>
       <c r="C22" t="n">
-        <v>2.022852659225464</v>
+        <v>2.388315439224243</v>
       </c>
       <c r="D22" t="n">
-        <v>1.992917537689209</v>
+        <v>2.277496576309204</v>
       </c>
       <c r="E22" t="n">
-        <v>1.96847128868103</v>
+        <v>2.315016746520996</v>
       </c>
       <c r="F22" t="n">
-        <v>2.086191415786743</v>
+        <v>2.378546953201294</v>
       </c>
       <c r="G22" t="n">
-        <v>2.028822183609009</v>
+        <v>2.229523658752441</v>
       </c>
       <c r="H22" t="n">
-        <v>2.071223020553589</v>
+        <v>2.361277341842651</v>
       </c>
       <c r="I22" t="n">
-        <v>2.056261777877808</v>
+        <v>2.109280586242676</v>
       </c>
       <c r="J22" t="n">
-        <v>1.954504251480103</v>
+        <v>2.340540409088135</v>
       </c>
       <c r="K22" t="n">
-        <v>2.119102954864502</v>
+        <v>2.270450353622437</v>
       </c>
       <c r="L22" t="n">
-        <v>2.03202006816864</v>
+        <v>2.29010705947876</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1.963998556137085</v>
+        <v>2.060899257659912</v>
       </c>
       <c r="C23" t="n">
-        <v>1.7550208568573</v>
+        <v>2.10899829864502</v>
       </c>
       <c r="D23" t="n">
-        <v>1.833831071853638</v>
+        <v>2.017512083053589</v>
       </c>
       <c r="E23" t="n">
-        <v>1.820353984832764</v>
+        <v>2.410139799118042</v>
       </c>
       <c r="F23" t="n">
-        <v>1.912616968154907</v>
+        <v>2.254652261734009</v>
       </c>
       <c r="G23" t="n">
-        <v>1.899664878845215</v>
+        <v>2.252828598022461</v>
       </c>
       <c r="H23" t="n">
-        <v>1.820358514785767</v>
+        <v>2.198879480361938</v>
       </c>
       <c r="I23" t="n">
-        <v>1.782463550567627</v>
+        <v>2.065451383590698</v>
       </c>
       <c r="J23" t="n">
-        <v>2.018857479095459</v>
+        <v>2.201722621917725</v>
       </c>
       <c r="K23" t="n">
-        <v>2.026832818984985</v>
+        <v>2.307210445404053</v>
       </c>
       <c r="L23" t="n">
-        <v>1.883399868011475</v>
+        <v>2.187829422950744</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1.948052883148193</v>
+        <v>2.134743452072144</v>
       </c>
       <c r="C24" t="n">
-        <v>1.975489139556885</v>
+        <v>2.328617572784424</v>
       </c>
       <c r="D24" t="n">
-        <v>1.835824489593506</v>
+        <v>2.178733110427856</v>
       </c>
       <c r="E24" t="n">
-        <v>1.923607587814331</v>
+        <v>2.11759352684021</v>
       </c>
       <c r="F24" t="n">
-        <v>1.926590204238892</v>
+        <v>2.241019248962402</v>
       </c>
       <c r="G24" t="n">
-        <v>1.97398567199707</v>
+        <v>2.101811647415161</v>
       </c>
       <c r="H24" t="n">
-        <v>1.921608924865723</v>
+        <v>2.186552762985229</v>
       </c>
       <c r="I24" t="n">
-        <v>1.903645753860474</v>
+        <v>2.382660627365112</v>
       </c>
       <c r="J24" t="n">
-        <v>2.072230100631714</v>
+        <v>2.167696714401245</v>
       </c>
       <c r="K24" t="n">
-        <v>1.824342250823975</v>
+        <v>2.393779516220093</v>
       </c>
       <c r="L24" t="n">
-        <v>1.930537700653076</v>
+        <v>2.223320817947388</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>2.127071857452393</v>
+        <v>2.431165218353271</v>
       </c>
       <c r="C25" t="n">
-        <v>2.065239191055298</v>
+        <v>2.392832040786743</v>
       </c>
       <c r="D25" t="n">
-        <v>1.947540998458862</v>
+        <v>2.187955856323242</v>
       </c>
       <c r="E25" t="n">
-        <v>2.071222066879272</v>
+        <v>2.179189682006836</v>
       </c>
       <c r="F25" t="n">
-        <v>2.072710037231445</v>
+        <v>2.227458477020264</v>
       </c>
       <c r="G25" t="n">
-        <v>1.973994731903076</v>
+        <v>2.46200704574585</v>
       </c>
       <c r="H25" t="n">
-        <v>1.916611194610596</v>
+        <v>2.370233774185181</v>
       </c>
       <c r="I25" t="n">
-        <v>2.104151725769043</v>
+        <v>2.163332939147949</v>
       </c>
       <c r="J25" t="n">
-        <v>2.182454824447632</v>
+        <v>2.364463806152344</v>
       </c>
       <c r="K25" t="n">
-        <v>1.983948707580566</v>
+        <v>2.625047445297241</v>
       </c>
       <c r="L25" t="n">
-        <v>2.044494533538818</v>
+        <v>2.340368628501892</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>2.694643020629883</v>
+        <v>2.603738784790039</v>
       </c>
       <c r="C26" t="n">
-        <v>2.273197174072266</v>
+        <v>2.526790142059326</v>
       </c>
       <c r="D26" t="n">
-        <v>2.444268226623535</v>
+        <v>2.436691999435425</v>
       </c>
       <c r="E26" t="n">
-        <v>2.376428604125977</v>
+        <v>2.420773029327393</v>
       </c>
       <c r="F26" t="n">
-        <v>2.19939136505127</v>
+        <v>2.508141756057739</v>
       </c>
       <c r="G26" t="n">
-        <v>2.078206062316895</v>
+        <v>2.663169145584106</v>
       </c>
       <c r="H26" t="n">
-        <v>2.13905143737793</v>
+        <v>2.4142746925354</v>
       </c>
       <c r="I26" t="n">
-        <v>2.251769065856934</v>
+        <v>2.446538686752319</v>
       </c>
       <c r="J26" t="n">
-        <v>2.303632974624634</v>
+        <v>2.669434547424316</v>
       </c>
       <c r="K26" t="n">
-        <v>2.452781200408936</v>
+        <v>2.551038980484009</v>
       </c>
       <c r="L26" t="n">
-        <v>2.321336913108826</v>
+        <v>2.524059176445007</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1.940065860748291</v>
+        <v>2.203193187713623</v>
       </c>
       <c r="C27" t="n">
-        <v>1.963490724563599</v>
+        <v>2.2086021900177</v>
       </c>
       <c r="D27" t="n">
-        <v>2.158499240875244</v>
+        <v>2.389378309249878</v>
       </c>
       <c r="E27" t="n">
-        <v>2.183454036712646</v>
+        <v>2.34285306930542</v>
       </c>
       <c r="F27" t="n">
-        <v>2.002905130386353</v>
+        <v>2.278442144393921</v>
       </c>
       <c r="G27" t="n">
-        <v>1.957531452178955</v>
+        <v>2.228665828704834</v>
       </c>
       <c r="H27" t="n">
-        <v>2.031813859939575</v>
+        <v>2.186520099639893</v>
       </c>
       <c r="I27" t="n">
-        <v>2.062244653701782</v>
+        <v>2.401760339736938</v>
       </c>
       <c r="J27" t="n">
-        <v>1.962008476257324</v>
+        <v>2.262137651443481</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1600022315979</v>
+        <v>2.215190649032593</v>
       </c>
       <c r="L27" t="n">
-        <v>2.042201566696167</v>
+        <v>2.271674346923828</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2.017855405807495</v>
+        <v>2.398238658905029</v>
       </c>
       <c r="C28" t="n">
-        <v>2.054268836975098</v>
+        <v>2.164505481719971</v>
       </c>
       <c r="D28" t="n">
-        <v>2.040789842605591</v>
+        <v>2.276517391204834</v>
       </c>
       <c r="E28" t="n">
-        <v>1.934571266174316</v>
+        <v>2.308612585067749</v>
       </c>
       <c r="F28" t="n">
-        <v>2.111631870269775</v>
+        <v>2.306941747665405</v>
       </c>
       <c r="G28" t="n">
-        <v>2.038795232772827</v>
+        <v>2.412383079528809</v>
       </c>
       <c r="H28" t="n">
-        <v>2.126086235046387</v>
+        <v>2.324508905410767</v>
       </c>
       <c r="I28" t="n">
-        <v>1.951027870178223</v>
+        <v>2.639116764068604</v>
       </c>
       <c r="J28" t="n">
-        <v>2.091659545898438</v>
+        <v>2.399930477142334</v>
       </c>
       <c r="K28" t="n">
-        <v>2.028361082077026</v>
+        <v>3.052009344100952</v>
       </c>
       <c r="L28" t="n">
-        <v>2.039504718780518</v>
+        <v>2.428276443481445</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>2.039792776107788</v>
+        <v>2.392931699752808</v>
       </c>
       <c r="C29" t="n">
-        <v>2.026828527450562</v>
+        <v>2.252465009689331</v>
       </c>
       <c r="D29" t="n">
-        <v>1.999897480010986</v>
+        <v>2.295833110809326</v>
       </c>
       <c r="E29" t="n">
-        <v>1.98893141746521</v>
+        <v>2.424194574356079</v>
       </c>
       <c r="F29" t="n">
-        <v>2.09017539024353</v>
+        <v>2.252182245254517</v>
       </c>
       <c r="G29" t="n">
-        <v>2.005887031555176</v>
+        <v>2.268319845199585</v>
       </c>
       <c r="H29" t="n">
-        <v>2.073224782943726</v>
+        <v>2.293987035751343</v>
       </c>
       <c r="I29" t="n">
-        <v>2.015864849090576</v>
+        <v>2.290550947189331</v>
       </c>
       <c r="J29" t="n">
-        <v>2.084703683853149</v>
+        <v>2.282463788986206</v>
       </c>
       <c r="K29" t="n">
-        <v>2.170475721359253</v>
+        <v>2.302600622177124</v>
       </c>
       <c r="L29" t="n">
-        <v>2.049578166007996</v>
+        <v>2.305552887916565</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>2.120109558105469</v>
+        <v>2.369611024856567</v>
       </c>
       <c r="C30" t="n">
-        <v>2.032689332962036</v>
+        <v>2.280614137649536</v>
       </c>
       <c r="D30" t="n">
-        <v>1.973482847213745</v>
+        <v>2.288934946060181</v>
       </c>
       <c r="E30" t="n">
-        <v>2.061247587203979</v>
+        <v>2.361819744110107</v>
       </c>
       <c r="F30" t="n">
-        <v>2.038800239562988</v>
+        <v>2.302942037582397</v>
       </c>
       <c r="G30" t="n">
-        <v>2.075219392776489</v>
+        <v>2.380477666854858</v>
       </c>
       <c r="H30" t="n">
-        <v>2.036801338195801</v>
+        <v>2.521868228912354</v>
       </c>
       <c r="I30" t="n">
-        <v>2.043303966522217</v>
+        <v>2.366979598999023</v>
       </c>
       <c r="J30" t="n">
-        <v>2.094658374786377</v>
+        <v>2.480096340179443</v>
       </c>
       <c r="K30" t="n">
-        <v>2.064247846603394</v>
+        <v>2.397907018661499</v>
       </c>
       <c r="L30" t="n">
-        <v>2.05405604839325</v>
+        <v>2.375125074386597</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1.721113443374634</v>
+        <v>2.160858631134033</v>
       </c>
       <c r="C31" t="n">
-        <v>1.814367294311523</v>
+        <v>1.942472457885742</v>
       </c>
       <c r="D31" t="n">
-        <v>1.776472091674805</v>
+        <v>2.068384408950806</v>
       </c>
       <c r="E31" t="n">
-        <v>1.727104902267456</v>
+        <v>2.040032148361206</v>
       </c>
       <c r="F31" t="n">
-        <v>1.767504453659058</v>
+        <v>2.13562536239624</v>
       </c>
       <c r="G31" t="n">
-        <v>1.736069202423096</v>
+        <v>2.039944887161255</v>
       </c>
       <c r="H31" t="n">
-        <v>1.898673057556152</v>
+        <v>1.946031332015991</v>
       </c>
       <c r="I31" t="n">
-        <v>1.754535675048828</v>
+        <v>1.999037981033325</v>
       </c>
       <c r="J31" t="n">
-        <v>1.720109939575195</v>
+        <v>1.999646425247192</v>
       </c>
       <c r="K31" t="n">
-        <v>1.723108053207397</v>
+        <v>1.96722412109375</v>
       </c>
       <c r="L31" t="n">
-        <v>1.763905811309814</v>
+        <v>2.029925775527954</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>2.088667154312134</v>
+        <v>2.222008466720581</v>
       </c>
       <c r="C32" t="n">
-        <v>2.065252542495728</v>
+        <v>2.14650821685791</v>
       </c>
       <c r="D32" t="n">
-        <v>2.196407794952393</v>
+        <v>2.363688468933105</v>
       </c>
       <c r="E32" t="n">
-        <v>2.056745529174805</v>
+        <v>2.224872350692749</v>
       </c>
       <c r="F32" t="n">
-        <v>1.934107065200806</v>
+        <v>2.183270215988159</v>
       </c>
       <c r="G32" t="n">
-        <v>2.128081321716309</v>
+        <v>2.184507608413696</v>
       </c>
       <c r="H32" t="n">
-        <v>2.076212882995605</v>
+        <v>2.206537961959839</v>
       </c>
       <c r="I32" t="n">
-        <v>2.03281569480896</v>
+        <v>2.18785834312439</v>
       </c>
       <c r="J32" t="n">
-        <v>2.005921602249146</v>
+        <v>2.29643702507019</v>
       </c>
       <c r="K32" t="n">
-        <v>2.189438819885254</v>
+        <v>2.210986614227295</v>
       </c>
       <c r="L32" t="n">
-        <v>2.077365040779114</v>
+        <v>2.222667527198792</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>2.143047094345093</v>
+        <v>2.281270265579224</v>
       </c>
       <c r="C33" t="n">
-        <v>2.058270215988159</v>
+        <v>2.249746561050415</v>
       </c>
       <c r="D33" t="n">
-        <v>2.05774998664856</v>
+        <v>2.067937850952148</v>
       </c>
       <c r="E33" t="n">
-        <v>1.972988367080688</v>
+        <v>2.209512948989868</v>
       </c>
       <c r="F33" t="n">
-        <v>1.923549175262451</v>
+        <v>2.154304981231689</v>
       </c>
       <c r="G33" t="n">
-        <v>2.082100868225098</v>
+        <v>2.351755142211914</v>
       </c>
       <c r="H33" t="n">
-        <v>2.167360782623291</v>
+        <v>2.320442914962769</v>
       </c>
       <c r="I33" t="n">
-        <v>1.938443899154663</v>
+        <v>2.416815996170044</v>
       </c>
       <c r="J33" t="n">
-        <v>1.946446180343628</v>
+        <v>2.147355794906616</v>
       </c>
       <c r="K33" t="n">
-        <v>1.952932596206665</v>
+        <v>2.239150047302246</v>
       </c>
       <c r="L33" t="n">
-        <v>2.02428891658783</v>
+        <v>2.243829250335693</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1.867130279541016</v>
+        <v>1.951034069061279</v>
       </c>
       <c r="C34" t="n">
-        <v>1.867645502090454</v>
+        <v>1.98700475692749</v>
       </c>
       <c r="D34" t="n">
-        <v>1.85468053817749</v>
+        <v>2.29803991317749</v>
       </c>
       <c r="E34" t="n">
-        <v>1.827237367630005</v>
+        <v>2.123479843139648</v>
       </c>
       <c r="F34" t="n">
-        <v>1.785361289978027</v>
+        <v>1.972704410552979</v>
       </c>
       <c r="G34" t="n">
-        <v>1.828234910964966</v>
+        <v>1.969764232635498</v>
       </c>
       <c r="H34" t="n">
-        <v>1.873143196105957</v>
+        <v>2.030570507049561</v>
       </c>
       <c r="I34" t="n">
-        <v>1.765401363372803</v>
+        <v>2.039867401123047</v>
       </c>
       <c r="J34" t="n">
-        <v>1.79134202003479</v>
+        <v>2.082825183868408</v>
       </c>
       <c r="K34" t="n">
-        <v>1.837224006652832</v>
+        <v>1.982529878616333</v>
       </c>
       <c r="L34" t="n">
-        <v>1.829740047454834</v>
+        <v>2.043782019615173</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2.533409833908081</v>
+        <v>2.537761926651001</v>
       </c>
       <c r="C35" t="n">
-        <v>2.363356113433838</v>
+        <v>2.542210817337036</v>
       </c>
       <c r="D35" t="n">
-        <v>2.190301418304443</v>
+        <v>2.486879348754883</v>
       </c>
       <c r="E35" t="n">
-        <v>2.213234663009644</v>
+        <v>2.512510538101196</v>
       </c>
       <c r="F35" t="n">
-        <v>2.334436893463135</v>
+        <v>2.502933740615845</v>
       </c>
       <c r="G35" t="n">
-        <v>2.270584583282471</v>
+        <v>2.524222135543823</v>
       </c>
       <c r="H35" t="n">
-        <v>2.207256317138672</v>
+        <v>2.495310306549072</v>
       </c>
       <c r="I35" t="n">
-        <v>2.251138925552368</v>
+        <v>2.510048627853394</v>
       </c>
       <c r="J35" t="n">
-        <v>2.411264419555664</v>
+        <v>2.566256761550903</v>
       </c>
       <c r="K35" t="n">
-        <v>2.193826198577881</v>
+        <v>2.573579788208008</v>
       </c>
       <c r="L35" t="n">
-        <v>2.29688093662262</v>
+        <v>2.525171399116516</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1.920002698898315</v>
+        <v>2.091901540756226</v>
       </c>
       <c r="C36" t="n">
-        <v>1.874118089675903</v>
+        <v>2.144295930862427</v>
       </c>
       <c r="D36" t="n">
-        <v>1.91251802444458</v>
+        <v>2.084161996841431</v>
       </c>
       <c r="E36" t="n">
-        <v>1.803305387496948</v>
+        <v>2.290051698684692</v>
       </c>
       <c r="F36" t="n">
-        <v>1.864649772644043</v>
+        <v>2.192444801330566</v>
       </c>
       <c r="G36" t="n">
-        <v>1.927487373352051</v>
+        <v>1.964155435562134</v>
       </c>
       <c r="H36" t="n">
-        <v>1.932473421096802</v>
+        <v>2.065527200698853</v>
       </c>
       <c r="I36" t="n">
-        <v>1.86463737487793</v>
+        <v>2.230523347854614</v>
       </c>
       <c r="J36" t="n">
-        <v>1.81428337097168</v>
+        <v>2.111073017120361</v>
       </c>
       <c r="K36" t="n">
-        <v>1.84770655632019</v>
+        <v>2.128084421157837</v>
       </c>
       <c r="L36" t="n">
-        <v>1.876118206977844</v>
+        <v>2.130221939086914</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>2.142917394638062</v>
+        <v>2.385085582733154</v>
       </c>
       <c r="C37" t="n">
-        <v>2.203269958496094</v>
+        <v>2.281080484390259</v>
       </c>
       <c r="D37" t="n">
-        <v>2.208270311355591</v>
+        <v>2.492871284484863</v>
       </c>
       <c r="E37" t="n">
-        <v>2.006776332855225</v>
+        <v>2.383303165435791</v>
       </c>
       <c r="F37" t="n">
-        <v>2.19429349899292</v>
+        <v>2.398096561431885</v>
       </c>
       <c r="G37" t="n">
-        <v>2.164380550384521</v>
+        <v>2.42585301399231</v>
       </c>
       <c r="H37" t="n">
-        <v>2.130973815917969</v>
+        <v>2.334687471389771</v>
       </c>
       <c r="I37" t="n">
-        <v>2.098040342330933</v>
+        <v>2.401553869247437</v>
       </c>
       <c r="J37" t="n">
-        <v>2.059657096862793</v>
+        <v>2.303446292877197</v>
       </c>
       <c r="K37" t="n">
-        <v>3.674044609069824</v>
+        <v>2.463418006896973</v>
       </c>
       <c r="L37" t="n">
-        <v>2.288262391090393</v>
+        <v>2.386939573287964</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>5.463937997817993</v>
+        <v>2.673860788345337</v>
       </c>
       <c r="C38" t="n">
-        <v>2.945369482040405</v>
+        <v>2.746664524078369</v>
       </c>
       <c r="D38" t="n">
-        <v>2.452616930007935</v>
+        <v>2.723081350326538</v>
       </c>
       <c r="E38" t="n">
-        <v>2.542877197265625</v>
+        <v>2.909255981445312</v>
       </c>
       <c r="F38" t="n">
-        <v>3.735370397567749</v>
+        <v>2.761276483535767</v>
       </c>
       <c r="G38" t="n">
-        <v>2.563832759857178</v>
+        <v>2.806069374084473</v>
       </c>
       <c r="H38" t="n">
-        <v>2.766801595687866</v>
+        <v>2.747738361358643</v>
       </c>
       <c r="I38" t="n">
-        <v>2.381815195083618</v>
+        <v>2.72552752494812</v>
       </c>
       <c r="J38" t="n">
-        <v>2.400754690170288</v>
+        <v>2.741018056869507</v>
       </c>
       <c r="K38" t="n">
-        <v>2.723422288894653</v>
+        <v>2.653445720672607</v>
       </c>
       <c r="L38" t="n">
-        <v>2.997679853439331</v>
+        <v>2.748793816566467</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>2.619194269180298</v>
+        <v>2.446716070175171</v>
       </c>
       <c r="C39" t="n">
-        <v>2.025727033615112</v>
+        <v>2.261945247650146</v>
       </c>
       <c r="D39" t="n">
-        <v>2.104027271270752</v>
+        <v>2.53166389465332</v>
       </c>
       <c r="E39" t="n">
-        <v>2.112996578216553</v>
+        <v>2.300459623336792</v>
       </c>
       <c r="F39" t="n">
-        <v>2.210250616073608</v>
+        <v>2.341026544570923</v>
       </c>
       <c r="G39" t="n">
-        <v>2.147416114807129</v>
+        <v>2.627053260803223</v>
       </c>
       <c r="H39" t="n">
-        <v>2.178823947906494</v>
+        <v>2.303869724273682</v>
       </c>
       <c r="I39" t="n">
-        <v>2.024237871170044</v>
+        <v>2.473917245864868</v>
       </c>
       <c r="J39" t="n">
-        <v>2.322455644607544</v>
+        <v>2.309301614761353</v>
       </c>
       <c r="K39" t="n">
-        <v>2.515615463256836</v>
+        <v>2.531766414642334</v>
       </c>
       <c r="L39" t="n">
-        <v>2.226074481010437</v>
+        <v>2.412771964073181</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>2.191296100616455</v>
+        <v>2.308300495147705</v>
       </c>
       <c r="C40" t="n">
-        <v>1.990816593170166</v>
+        <v>2.382286548614502</v>
       </c>
       <c r="D40" t="n">
-        <v>2.183852195739746</v>
+        <v>2.250098943710327</v>
       </c>
       <c r="E40" t="n">
-        <v>2.209762334823608</v>
+        <v>2.231175184249878</v>
       </c>
       <c r="F40" t="n">
-        <v>2.120982646942139</v>
+        <v>2.207893848419189</v>
       </c>
       <c r="G40" t="n">
-        <v>2.081583499908447</v>
+        <v>2.41145396232605</v>
       </c>
       <c r="H40" t="n">
-        <v>2.01726222038269</v>
+        <v>2.292887687683105</v>
       </c>
       <c r="I40" t="n">
-        <v>1.985337257385254</v>
+        <v>2.220597743988037</v>
       </c>
       <c r="J40" t="n">
-        <v>2.14443039894104</v>
+        <v>2.351590871810913</v>
       </c>
       <c r="K40" t="n">
-        <v>2.134981393814087</v>
+        <v>2.326840877532959</v>
       </c>
       <c r="L40" t="n">
-        <v>2.106030464172363</v>
+        <v>2.298312616348267</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>2.437889814376831</v>
+        <v>2.438982009887695</v>
       </c>
       <c r="C41" t="n">
-        <v>2.098208427429199</v>
+        <v>2.486933469772339</v>
       </c>
       <c r="D41" t="n">
-        <v>2.226835966110229</v>
+        <v>2.486245393753052</v>
       </c>
       <c r="E41" t="n">
-        <v>2.340528011322021</v>
+        <v>2.584330320358276</v>
       </c>
       <c r="F41" t="n">
-        <v>2.201389312744141</v>
+        <v>2.518816709518433</v>
       </c>
       <c r="G41" t="n">
-        <v>2.289679288864136</v>
+        <v>2.433768272399902</v>
       </c>
       <c r="H41" t="n">
-        <v>2.195408344268799</v>
+        <v>2.46121072769165</v>
       </c>
       <c r="I41" t="n">
-        <v>2.147021055221558</v>
+        <v>2.431600332260132</v>
       </c>
       <c r="J41" t="n">
-        <v>2.146024942398071</v>
+        <v>2.591174364089966</v>
       </c>
       <c r="K41" t="n">
-        <v>2.124595403671265</v>
+        <v>2.420573949813843</v>
       </c>
       <c r="L41" t="n">
-        <v>2.220758056640625</v>
+        <v>2.485363554954529</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>1.975456714630127</v>
+        <v>2.139036178588867</v>
       </c>
       <c r="C42" t="n">
-        <v>1.910650253295898</v>
+        <v>2.09227466583252</v>
       </c>
       <c r="D42" t="n">
-        <v>1.966988086700439</v>
+        <v>2.233994722366333</v>
       </c>
       <c r="E42" t="n">
-        <v>1.95451807975769</v>
+        <v>2.127810478210449</v>
       </c>
       <c r="F42" t="n">
-        <v>1.996918439865112</v>
+        <v>2.035664796829224</v>
       </c>
       <c r="G42" t="n">
-        <v>1.899657726287842</v>
+        <v>2.182787418365479</v>
       </c>
       <c r="H42" t="n">
-        <v>1.963030338287354</v>
+        <v>2.155227184295654</v>
       </c>
       <c r="I42" t="n">
-        <v>1.865750789642334</v>
+        <v>2.227166175842285</v>
       </c>
       <c r="J42" t="n">
-        <v>1.940565347671509</v>
+        <v>2.134628772735596</v>
       </c>
       <c r="K42" t="n">
-        <v>1.891686916351318</v>
+        <v>2.066580772399902</v>
       </c>
       <c r="L42" t="n">
-        <v>1.936522269248962</v>
+        <v>2.139517116546631</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>2.085191249847412</v>
+        <v>2.238485097885132</v>
       </c>
       <c r="C43" t="n">
-        <v>2.334543466567993</v>
+        <v>2.497144460678101</v>
       </c>
       <c r="D43" t="n">
-        <v>2.014857769012451</v>
+        <v>2.336486339569092</v>
       </c>
       <c r="E43" t="n">
-        <v>2.116113662719727</v>
+        <v>2.660398244857788</v>
       </c>
       <c r="F43" t="n">
-        <v>2.185433864593506</v>
+        <v>3.574291706085205</v>
       </c>
       <c r="G43" t="n">
-        <v>1.998904466629028</v>
+        <v>2.975005388259888</v>
       </c>
       <c r="H43" t="n">
-        <v>1.98095440864563</v>
+        <v>2.909714460372925</v>
       </c>
       <c r="I43" t="n">
-        <v>2.107124328613281</v>
+        <v>2.873623609542847</v>
       </c>
       <c r="J43" t="n">
-        <v>2.11111855506897</v>
+        <v>2.692052364349365</v>
       </c>
       <c r="K43" t="n">
-        <v>2.275206089019775</v>
+        <v>2.531400680541992</v>
       </c>
       <c r="L43" t="n">
-        <v>2.120944786071777</v>
+        <v>2.728860235214233</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1.975983381271362</v>
+        <v>2.314613342285156</v>
       </c>
       <c r="C44" t="n">
-        <v>1.996906995773315</v>
+        <v>2.412376165390015</v>
       </c>
       <c r="D44" t="n">
-        <v>2.178450584411621</v>
+        <v>2.411562919616699</v>
       </c>
       <c r="E44" t="n">
-        <v>2.153013706207275</v>
+        <v>2.342367649078369</v>
       </c>
       <c r="F44" t="n">
-        <v>2.027829647064209</v>
+        <v>2.154803514480591</v>
       </c>
       <c r="G44" t="n">
-        <v>2.074219942092896</v>
+        <v>2.361905574798584</v>
       </c>
       <c r="H44" t="n">
-        <v>2.013872623443604</v>
+        <v>2.266724109649658</v>
       </c>
       <c r="I44" t="n">
-        <v>2.004907608032227</v>
+        <v>2.363673448562622</v>
       </c>
       <c r="J44" t="n">
-        <v>1.977967023849487</v>
+        <v>2.261835098266602</v>
       </c>
       <c r="K44" t="n">
-        <v>1.864747524261475</v>
+        <v>2.294654846191406</v>
       </c>
       <c r="L44" t="n">
-        <v>2.026789903640747</v>
+        <v>2.31845166683197</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1.895667552947998</v>
+        <v>2.095247507095337</v>
       </c>
       <c r="C45" t="n">
-        <v>1.771500110626221</v>
+        <v>2.191853761672974</v>
       </c>
       <c r="D45" t="n">
-        <v>1.797438383102417</v>
+        <v>2.21513843536377</v>
       </c>
       <c r="E45" t="n">
-        <v>1.919612169265747</v>
+        <v>2.115063428878784</v>
       </c>
       <c r="F45" t="n">
-        <v>1.824348211288452</v>
+        <v>2.123548030853271</v>
       </c>
       <c r="G45" t="n">
-        <v>1.781457424163818</v>
+        <v>2.014848232269287</v>
       </c>
       <c r="H45" t="n">
-        <v>1.916624069213867</v>
+        <v>2.177386283874512</v>
       </c>
       <c r="I45" t="n">
-        <v>1.777482509613037</v>
+        <v>2.09052586555481</v>
       </c>
       <c r="J45" t="n">
-        <v>1.948522329330444</v>
+        <v>2.027072906494141</v>
       </c>
       <c r="K45" t="n">
-        <v>1.941058874130249</v>
+        <v>2.212923765182495</v>
       </c>
       <c r="L45" t="n">
-        <v>1.857371163368225</v>
+        <v>2.126360821723938</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>2.097178220748901</v>
+        <v>2.058329582214355</v>
       </c>
       <c r="C46" t="n">
-        <v>1.844301223754883</v>
+        <v>2.038009643554688</v>
       </c>
       <c r="D46" t="n">
-        <v>1.685203313827515</v>
+        <v>1.968973159790039</v>
       </c>
       <c r="E46" t="n">
-        <v>1.709144353866577</v>
+        <v>1.851047515869141</v>
       </c>
       <c r="F46" t="n">
-        <v>1.785445690155029</v>
+        <v>2.271001100540161</v>
       </c>
       <c r="G46" t="n">
-        <v>1.904646396636963</v>
+        <v>2.120711088180542</v>
       </c>
       <c r="H46" t="n">
-        <v>1.687202453613281</v>
+        <v>1.973181009292603</v>
       </c>
       <c r="I46" t="n">
-        <v>1.682701587677002</v>
+        <v>1.933972120285034</v>
       </c>
       <c r="J46" t="n">
-        <v>1.882713079452515</v>
+        <v>2.158090353012085</v>
       </c>
       <c r="K46" t="n">
-        <v>1.722105979919434</v>
+        <v>2.129256010055542</v>
       </c>
       <c r="L46" t="n">
-        <v>1.80006422996521</v>
+        <v>2.050257158279419</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>2.771451234817505</v>
+        <v>3.200175523757935</v>
       </c>
       <c r="C47" t="n">
-        <v>2.539530515670776</v>
+        <v>3.103816986083984</v>
       </c>
       <c r="D47" t="n">
-        <v>2.540015935897827</v>
+        <v>2.738764524459839</v>
       </c>
       <c r="E47" t="n">
-        <v>2.495140790939331</v>
+        <v>2.846662044525146</v>
       </c>
       <c r="F47" t="n">
-        <v>2.452752590179443</v>
+        <v>2.994659662246704</v>
       </c>
       <c r="G47" t="n">
-        <v>2.342049598693848</v>
+        <v>3.388475179672241</v>
       </c>
       <c r="H47" t="n">
-        <v>2.622322797775269</v>
+        <v>2.958976984024048</v>
       </c>
       <c r="I47" t="n">
-        <v>2.78139328956604</v>
+        <v>2.761867761611938</v>
       </c>
       <c r="J47" t="n">
-        <v>2.581416130065918</v>
+        <v>2.952145099639893</v>
       </c>
       <c r="K47" t="n">
-        <v>2.52407169342041</v>
+        <v>3.037418365478516</v>
       </c>
       <c r="L47" t="n">
-        <v>2.565014457702637</v>
+        <v>2.998296213150025</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>2.009881258010864</v>
+        <v>2.30194354057312</v>
       </c>
       <c r="C48" t="n">
-        <v>2.017373085021973</v>
+        <v>2.284583568572998</v>
       </c>
       <c r="D48" t="n">
-        <v>2.117105007171631</v>
+        <v>2.354543924331665</v>
       </c>
       <c r="E48" t="n">
-        <v>2.115110158920288</v>
+        <v>2.329996347427368</v>
       </c>
       <c r="F48" t="n">
-        <v>2.11211371421814</v>
+        <v>2.439965009689331</v>
       </c>
       <c r="G48" t="n">
-        <v>2.143039703369141</v>
+        <v>2.311307430267334</v>
       </c>
       <c r="H48" t="n">
-        <v>2.06425404548645</v>
+        <v>2.331507921218872</v>
       </c>
       <c r="I48" t="n">
-        <v>2.156002998352051</v>
+        <v>2.371136665344238</v>
       </c>
       <c r="J48" t="n">
-        <v>2.147526502609253</v>
+        <v>2.399805068969727</v>
       </c>
       <c r="K48" t="n">
-        <v>2.021845579147339</v>
+        <v>2.392861127853394</v>
       </c>
       <c r="L48" t="n">
-        <v>2.090425205230713</v>
+        <v>2.351765060424805</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>2.215357303619385</v>
+        <v>2.418417453765869</v>
       </c>
       <c r="C49" t="n">
-        <v>2.272701978683472</v>
+        <v>2.414624452590942</v>
       </c>
       <c r="D49" t="n">
-        <v>2.325579404830933</v>
+        <v>2.469454288482666</v>
       </c>
       <c r="E49" t="n">
-        <v>2.196411371231079</v>
+        <v>2.646392345428467</v>
       </c>
       <c r="F49" t="n">
-        <v>2.371442794799805</v>
+        <v>2.425796985626221</v>
       </c>
       <c r="G49" t="n">
-        <v>2.419357776641846</v>
+        <v>2.450297832489014</v>
       </c>
       <c r="H49" t="n">
-        <v>2.48068642616272</v>
+        <v>2.436286211013794</v>
       </c>
       <c r="I49" t="n">
-        <v>2.267728567123413</v>
+        <v>2.336896419525146</v>
       </c>
       <c r="J49" t="n">
-        <v>2.173460006713867</v>
+        <v>2.467253923416138</v>
       </c>
       <c r="K49" t="n">
-        <v>2.205373764038086</v>
+        <v>2.616969108581543</v>
       </c>
       <c r="L49" t="n">
-        <v>2.292809939384461</v>
+        <v>2.46823890209198</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1.907648086547852</v>
+        <v>2.149742603302002</v>
       </c>
       <c r="C50" t="n">
-        <v>1.969483137130737</v>
+        <v>2.308209180831909</v>
       </c>
       <c r="D50" t="n">
-        <v>1.956019163131714</v>
+        <v>2.197554349899292</v>
       </c>
       <c r="E50" t="n">
-        <v>1.98495078086853</v>
+        <v>2.307045936584473</v>
       </c>
       <c r="F50" t="n">
-        <v>1.877726078033447</v>
+        <v>2.188549757003784</v>
       </c>
       <c r="G50" t="n">
-        <v>1.741050720214844</v>
+        <v>2.185659885406494</v>
       </c>
       <c r="H50" t="n">
-        <v>1.846290349960327</v>
+        <v>2.204236030578613</v>
       </c>
       <c r="I50" t="n">
-        <v>2.018854856491089</v>
+        <v>2.181588411331177</v>
       </c>
       <c r="J50" t="n">
-        <v>1.952038764953613</v>
+        <v>2.328761577606201</v>
       </c>
       <c r="K50" t="n">
-        <v>1.899654865264893</v>
+        <v>2.171216011047363</v>
       </c>
       <c r="L50" t="n">
-        <v>1.915371680259705</v>
+        <v>2.222256374359131</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1.867740392684937</v>
+        <v>2.160435199737549</v>
       </c>
       <c r="C51" t="n">
-        <v>1.857255220413208</v>
+        <v>2.048481225967407</v>
       </c>
       <c r="D51" t="n">
-        <v>1.973981380462646</v>
+        <v>2.055200099945068</v>
       </c>
       <c r="E51" t="n">
-        <v>1.874249935150146</v>
+        <v>2.324404954910278</v>
       </c>
       <c r="F51" t="n">
-        <v>1.875718355178833</v>
+        <v>2.172653436660767</v>
       </c>
       <c r="G51" t="n">
-        <v>1.810392141342163</v>
+        <v>2.128338813781738</v>
       </c>
       <c r="H51" t="n">
-        <v>1.953028202056885</v>
+        <v>2.063292503356934</v>
       </c>
       <c r="I51" t="n">
-        <v>1.921599149703979</v>
+        <v>2.095724821090698</v>
       </c>
       <c r="J51" t="n">
-        <v>1.917642831802368</v>
+        <v>2.198350429534912</v>
       </c>
       <c r="K51" t="n">
-        <v>1.772477865219116</v>
+        <v>2.148286104202271</v>
       </c>
       <c r="L51" t="n">
-        <v>1.882408547401428</v>
+        <v>2.139516758918762</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.224202890396118</v>
+        <v>2.329682726860046</v>
       </c>
       <c r="C52" t="n">
-        <v>2.122722206115723</v>
+        <v>2.336663222312927</v>
       </c>
       <c r="D52" t="n">
-        <v>2.165512685775757</v>
+        <v>2.342249612808228</v>
       </c>
       <c r="E52" t="n">
-        <v>2.111191258430481</v>
+        <v>2.364867067337036</v>
       </c>
       <c r="F52" t="n">
-        <v>2.133985185623169</v>
+        <v>2.369044156074524</v>
       </c>
       <c r="G52" t="n">
-        <v>2.107678718566894</v>
+        <v>2.393901281356812</v>
       </c>
       <c r="H52" t="n">
-        <v>2.108400392532348</v>
+        <v>2.381487317085266</v>
       </c>
       <c r="I52" t="n">
-        <v>2.104514112472534</v>
+        <v>2.374466581344604</v>
       </c>
       <c r="J52" t="n">
-        <v>2.103590941429138</v>
+        <v>2.411684918403625</v>
       </c>
       <c r="K52" t="n">
-        <v>2.145813121795654</v>
+        <v>2.407472009658814</v>
       </c>
       <c r="L52" t="n">
-        <v>2.132761151313781</v>
+        <v>2.371151889324188</v>
       </c>
     </row>
   </sheetData>
